--- a/output/roomself_excel/14317.xlsx
+++ b/output/roomself_excel/14317.xlsx
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>157850</v>
+        <v>239080</v>
       </c>
       <c r="D3" t="n">
-        <v>3180</v>
+        <v>3944</v>
       </c>
       <c r="E3" t="n">
-        <v>435</v>
+        <v>581</v>
       </c>
       <c r="F3" t="n">
-        <v>407</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>161823</v>
+        <v>32224</v>
       </c>
       <c r="D4" t="n">
-        <v>3296</v>
+        <v>1456</v>
       </c>
       <c r="E4" t="n">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44082</v>
+        <v>117031</v>
       </c>
       <c r="D5" t="n">
-        <v>1748</v>
+        <v>2764</v>
       </c>
       <c r="E5" t="n">
-        <v>867</v>
+        <v>423</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>155820</v>
+        <v>70841</v>
       </c>
       <c r="D6" t="n">
-        <v>3164</v>
+        <v>2412</v>
       </c>
       <c r="E6" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="F6" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32224</v>
+        <v>44082</v>
       </c>
       <c r="D7" t="n">
-        <v>1456</v>
+        <v>1748</v>
       </c>
       <c r="E7" t="n">
-        <v>461</v>
+        <v>158</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13348</v>
+        <v>21840</v>
       </c>
       <c r="D8" t="n">
-        <v>944</v>
+        <v>1376</v>
       </c>
       <c r="E8" t="n">
-        <v>468</v>
+        <v>296</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32184</v>
+        <v>140958</v>
       </c>
       <c r="D9" t="n">
-        <v>1624</v>
+        <v>5155</v>
       </c>
       <c r="E9" t="n">
-        <v>541</v>
+        <v>663</v>
       </c>
       <c r="F9" t="n">
-        <v>536</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>154253</v>
+        <v>162871</v>
       </c>
       <c r="D10" t="n">
-        <v>3508</v>
+        <v>3488</v>
       </c>
       <c r="E10" t="n">
-        <v>470</v>
+        <v>625</v>
       </c>
       <c r="F10" t="n">
-        <v>445</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70841</v>
+        <v>157850</v>
       </c>
       <c r="D11" t="n">
-        <v>2412</v>
+        <v>3180</v>
       </c>
       <c r="E11" t="n">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="F11" t="n">
-        <v>312</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239080</v>
+        <v>161823</v>
       </c>
       <c r="D12" t="n">
-        <v>3944</v>
+        <v>3296</v>
       </c>
       <c r="E12" t="n">
-        <v>875</v>
+        <v>515</v>
       </c>
       <c r="F12" t="n">
-        <v>581</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30098</v>
+        <v>155820</v>
       </c>
       <c r="D13" t="n">
-        <v>1596</v>
+        <v>3164</v>
       </c>
       <c r="E13" t="n">
-        <v>270</v>
+        <v>439</v>
       </c>
       <c r="F13" t="n">
-        <v>173</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>145715</v>
+        <v>13348</v>
       </c>
       <c r="D14" t="n">
-        <v>5032</v>
+        <v>944</v>
       </c>
       <c r="E14" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10504</v>
+        <v>32184</v>
       </c>
       <c r="D15" t="n">
-        <v>820</v>
+        <v>1624</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10956</v>
+        <v>154253</v>
       </c>
       <c r="D16" t="n">
-        <v>928</v>
+        <v>3508</v>
       </c>
       <c r="E16" t="n">
-        <v>377</v>
+        <v>470</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>117031</v>
+        <v>30098</v>
       </c>
       <c r="D17" t="n">
-        <v>2764</v>
+        <v>1596</v>
       </c>
       <c r="E17" t="n">
-        <v>423</v>
+        <v>270</v>
       </c>
       <c r="F17" t="n">
-        <v>398</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52742</v>
+        <v>145715</v>
       </c>
       <c r="D18" t="n">
-        <v>1916</v>
+        <v>5032</v>
       </c>
       <c r="E18" t="n">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>99553</v>
+        <v>10504</v>
       </c>
       <c r="D19" t="n">
-        <v>3264</v>
+        <v>820</v>
       </c>
       <c r="E19" t="n">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="F19" t="n">
-        <v>496</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21840</v>
+        <v>10956</v>
       </c>
       <c r="D20" t="n">
-        <v>1376</v>
+        <v>928</v>
       </c>
       <c r="E20" t="n">
-        <v>296</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8090</v>
+        <v>52742</v>
       </c>
       <c r="D21" t="n">
-        <v>842</v>
+        <v>1916</v>
       </c>
       <c r="E21" t="n">
-        <v>397</v>
+        <v>207</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14530</v>
+        <v>99553</v>
       </c>
       <c r="D22" t="n">
-        <v>1060</v>
+        <v>3264</v>
       </c>
       <c r="E22" t="n">
-        <v>620</v>
+        <v>534</v>
       </c>
       <c r="F22" t="n">
-        <v>412</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>140958</v>
+        <v>8090</v>
       </c>
       <c r="D23" t="n">
-        <v>5155</v>
+        <v>842</v>
       </c>
       <c r="E23" t="n">
-        <v>1022</v>
+        <v>124</v>
       </c>
       <c r="F23" t="n">
-        <v>948</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>162871</v>
+        <v>14530</v>
       </c>
       <c r="D24" t="n">
-        <v>3488</v>
+        <v>1060</v>
       </c>
       <c r="E24" t="n">
-        <v>1107</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">

--- a/output/roomself_excel/14317.xlsx
+++ b/output/roomself_excel/14317.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>3548</v>
       </c>
-      <c r="E2" t="n">
-        <v>524</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>407</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>385</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,34 @@
       <c r="D3" t="n">
         <v>3944</v>
       </c>
-      <c r="E3" t="n">
-        <v>581</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>455</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>556</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +613,18 @@
       <c r="D4" t="n">
         <v>1456</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +641,34 @@
       <c r="D5" t="n">
         <v>2764</v>
       </c>
-      <c r="E5" t="n">
-        <v>423</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>398</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>362</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +685,26 @@
       <c r="D6" t="n">
         <v>2412</v>
       </c>
-      <c r="E6" t="n">
-        <v>455</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>312</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +721,26 @@
       <c r="D7" t="n">
         <v>1748</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>158</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>14</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +757,34 @@
       <c r="D8" t="n">
         <v>1376</v>
       </c>
-      <c r="E8" t="n">
-        <v>296</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>260</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +801,26 @@
       <c r="D9" t="n">
         <v>5155</v>
       </c>
-      <c r="E9" t="n">
-        <v>663</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>342</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +837,34 @@
       <c r="D10" t="n">
         <v>3488</v>
       </c>
-      <c r="E10" t="n">
-        <v>625</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>306</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>601</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +881,34 @@
       <c r="D11" t="n">
         <v>3180</v>
       </c>
-      <c r="E11" t="n">
-        <v>435</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>407</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>385</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +925,34 @@
       <c r="D12" t="n">
         <v>3296</v>
       </c>
-      <c r="E12" t="n">
-        <v>515</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>350</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>501</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +969,34 @@
       <c r="D13" t="n">
         <v>3164</v>
       </c>
-      <c r="E13" t="n">
-        <v>439</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>385</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>371</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1013,18 @@
       <c r="D14" t="n">
         <v>944</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1041,18 @@
       <c r="D15" t="n">
         <v>1624</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1069,34 @@
       <c r="D16" t="n">
         <v>3508</v>
       </c>
-      <c r="E16" t="n">
-        <v>470</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>445</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>426</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1113,34 @@
       <c r="D17" t="n">
         <v>1596</v>
       </c>
-      <c r="E17" t="n">
-        <v>270</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>173</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>151</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1157,34 @@
       <c r="D18" t="n">
         <v>5032</v>
       </c>
-      <c r="E18" t="n">
-        <v>518</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>331</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>491</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1201,26 @@
       <c r="D19" t="n">
         <v>820</v>
       </c>
-      <c r="E19" t="n">
-        <v>104</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1237,34 @@
       <c r="D20" t="n">
         <v>928</v>
       </c>
-      <c r="E20" t="n">
-        <v>88</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>66</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1281,26 @@
       <c r="D21" t="n">
         <v>1916</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>207</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>36</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1317,42 @@
       <c r="D22" t="n">
         <v>3264</v>
       </c>
-      <c r="E22" t="n">
-        <v>534</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>342</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G22" t="n">
+        <v>36</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>121</v>
+      </c>
+      <c r="J22" t="n">
+        <v>43</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>102</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1369,26 @@
       <c r="D23" t="n">
         <v>842</v>
       </c>
-      <c r="E23" t="n">
-        <v>124</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>115</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1405,18 @@
       <c r="D24" t="n">
         <v>1060</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1433,49 @@
       <c r="D25" t="n">
         <v>2576</v>
       </c>
-      <c r="E25" t="n">
-        <v>459</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>252</v>
+        <v>142</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>216</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>128</v>
+      </c>
+      <c r="M25" t="n">
+        <v>14</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>428</v>
+      </c>
+      <c r="P25" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
